--- a/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FD37226-D539-4E96-AD90-BE13A418A68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BBC1260-081E-45CD-8842-6A207162B613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2774,7 +2774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D88839D4-C3E9-4013-9F94-6BC610B30FF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80187DA8-DE87-45F7-8106-934EB0A71E4B}">
   <dimension ref="B2:AF348"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8941,7 +8941,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B89291-B073-4035-9DC3-F93C8F216AA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF731E96-B54D-44CD-8025-E4C36E30F614}">
   <dimension ref="B9:L25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18520,7 +18520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F84D5EC-69F6-4755-B54A-72F3747607CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF53590-BAA4-4A25-A17B-FD52B9EB4FF4}">
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
